--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20261014.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20261014.xlsx
@@ -777,17 +777,17 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>崇越科技</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>616,000</t>
+          <t>7,137,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -799,17 +799,17 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>崇越科技</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>7,137,000</t>
+          <t>616,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>光寶科技</t>
+          <t>至上電子</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>7,991,000</t>
+          <t>26,620,004</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>至上電子</t>
+          <t>光寶科技</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>26,620,004</t>
+          <t>7,991,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
